--- a/Team-Data/2013-14/2-18-2013-14.xlsx
+++ b/Team-Data/2013-14/2-18-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E2" t="n">
         <v>25</v>
       </c>
       <c r="F2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G2" t="n">
-        <v>0.481</v>
+        <v>0.49</v>
       </c>
       <c r="H2" t="n">
         <v>48.5</v>
@@ -679,19 +746,19 @@
         <v>37.8</v>
       </c>
       <c r="J2" t="n">
-        <v>82.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K2" t="n">
         <v>0.459</v>
       </c>
       <c r="L2" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M2" t="n">
         <v>24.8</v>
       </c>
       <c r="N2" t="n">
-        <v>0.373</v>
+        <v>0.371</v>
       </c>
       <c r="O2" t="n">
         <v>16.5</v>
@@ -700,31 +767,31 @@
         <v>21.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.777</v>
+        <v>0.779</v>
       </c>
       <c r="R2" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="S2" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="T2" t="n">
-        <v>40.8</v>
+        <v>40.7</v>
       </c>
       <c r="U2" t="n">
         <v>25.6</v>
       </c>
       <c r="V2" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="W2" t="n">
         <v>8.9</v>
       </c>
       <c r="X2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z2" t="n">
         <v>18.8</v>
@@ -733,13 +800,13 @@
         <v>19.2</v>
       </c>
       <c r="AB2" t="n">
-        <v>101.3</v>
+        <v>101.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AE2" t="n">
         <v>14</v>
@@ -751,7 +818,7 @@
         <v>14</v>
       </c>
       <c r="AH2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI2" t="n">
         <v>15</v>
@@ -760,7 +827,7 @@
         <v>18</v>
       </c>
       <c r="AK2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL2" t="n">
         <v>4</v>
@@ -775,34 +842,34 @@
         <v>21</v>
       </c>
       <c r="AP2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ2" t="n">
         <v>6</v>
       </c>
       <c r="AR2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS2" t="n">
         <v>17</v>
       </c>
       <c r="AT2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AU2" t="n">
         <v>1</v>
       </c>
       <c r="AV2" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AW2" t="n">
         <v>4</v>
       </c>
       <c r="AX2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ2" t="n">
         <v>4</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-18-2013-14</t>
+          <t>2014-02-18</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>-3.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE3" t="n">
         <v>24</v>
@@ -933,16 +1000,16 @@
         <v>25</v>
       </c>
       <c r="AH3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ3" t="n">
         <v>13</v>
       </c>
       <c r="AK3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL3" t="n">
         <v>25</v>
@@ -966,7 +1033,7 @@
         <v>13</v>
       </c>
       <c r="AS3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT3" t="n">
         <v>15</v>
@@ -975,10 +1042,10 @@
         <v>26</v>
       </c>
       <c r="AV3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AW3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX3" t="n">
         <v>15</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-18-2013-14</t>
+          <t>2014-02-18</t>
         </is>
       </c>
     </row>
@@ -1103,13 +1170,13 @@
         <v>-2.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AE4" t="n">
         <v>17</v>
       </c>
       <c r="AF4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG4" t="n">
         <v>17</v>
@@ -1127,13 +1194,13 @@
         <v>14</v>
       </c>
       <c r="AL4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AM4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AN4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO4" t="n">
         <v>9</v>
@@ -1142,7 +1209,7 @@
         <v>8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR4" t="n">
         <v>26</v>
@@ -1157,7 +1224,7 @@
         <v>20</v>
       </c>
       <c r="AV4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW4" t="n">
         <v>12</v>
@@ -1175,10 +1242,10 @@
         <v>11</v>
       </c>
       <c r="BB4" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC4" t="n">
         <v>21</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>22</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-18-2013-14</t>
+          <t>2014-02-18</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F5" t="n">
         <v>30</v>
       </c>
       <c r="G5" t="n">
-        <v>0.444</v>
+        <v>0.434</v>
       </c>
       <c r="H5" t="n">
         <v>48.4</v>
@@ -1225,10 +1292,10 @@
         <v>35.6</v>
       </c>
       <c r="J5" t="n">
-        <v>81.40000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="K5" t="n">
-        <v>0.438</v>
+        <v>0.437</v>
       </c>
       <c r="L5" t="n">
         <v>5.8</v>
@@ -1237,31 +1304,31 @@
         <v>16.3</v>
       </c>
       <c r="N5" t="n">
-        <v>0.354</v>
+        <v>0.353</v>
       </c>
       <c r="O5" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="P5" t="n">
-        <v>24.8</v>
+        <v>24.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.723</v>
+        <v>0.726</v>
       </c>
       <c r="R5" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="S5" t="n">
-        <v>33.1</v>
+        <v>33</v>
       </c>
       <c r="T5" t="n">
         <v>42</v>
       </c>
       <c r="U5" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="V5" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="W5" t="n">
         <v>6.2</v>
@@ -1276,28 +1343,28 @@
         <v>18.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AB5" t="n">
-        <v>95</v>
+        <v>94.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.1</v>
+        <v>-2.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AF5" t="n">
         <v>20</v>
       </c>
       <c r="AG5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI5" t="n">
         <v>27</v>
@@ -1306,7 +1373,7 @@
         <v>24</v>
       </c>
       <c r="AK5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL5" t="n">
         <v>29</v>
@@ -1321,13 +1388,13 @@
         <v>13</v>
       </c>
       <c r="AP5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AQ5" t="n">
         <v>27</v>
       </c>
       <c r="AR5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AS5" t="n">
         <v>8</v>
@@ -1348,7 +1415,7 @@
         <v>11</v>
       </c>
       <c r="AY5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ5" t="n">
         <v>3</v>
@@ -1360,7 +1427,7 @@
         <v>26</v>
       </c>
       <c r="BC5" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-18-2013-14</t>
+          <t>2014-02-18</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>-0.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
@@ -1509,10 +1576,10 @@
         <v>10</v>
       </c>
       <c r="AR6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT6" t="n">
         <v>9</v>
@@ -1536,7 +1603,7 @@
         <v>5</v>
       </c>
       <c r="BA6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB6" t="n">
         <v>30</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-18-2013-14</t>
+          <t>2014-02-18</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F7" t="n">
         <v>33</v>
       </c>
       <c r="G7" t="n">
-        <v>0.389</v>
+        <v>0.377</v>
       </c>
       <c r="H7" t="n">
         <v>48.8</v>
@@ -1595,37 +1662,37 @@
         <v>0.425</v>
       </c>
       <c r="L7" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="M7" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="N7" t="n">
         <v>0.358</v>
       </c>
       <c r="O7" t="n">
-        <v>17</v>
+        <v>16.8</v>
       </c>
       <c r="P7" t="n">
-        <v>22.9</v>
+        <v>22.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.742</v>
+        <v>0.739</v>
       </c>
       <c r="R7" t="n">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="S7" t="n">
-        <v>31.6</v>
+        <v>31.5</v>
       </c>
       <c r="T7" t="n">
-        <v>44.4</v>
+        <v>44.1</v>
       </c>
       <c r="U7" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V7" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="W7" t="n">
         <v>7.4</v>
@@ -1634,31 +1701,31 @@
         <v>3.9</v>
       </c>
       <c r="Y7" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Z7" t="n">
         <v>20.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>97</v>
+        <v>96.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>-4.7</v>
+        <v>-5.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE7" t="n">
         <v>22</v>
       </c>
       <c r="AF7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH7" t="n">
         <v>2</v>
@@ -1676,25 +1743,25 @@
         <v>19</v>
       </c>
       <c r="AM7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AN7" t="n">
         <v>15</v>
       </c>
       <c r="AO7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AP7" t="n">
         <v>18</v>
       </c>
-      <c r="AP7" t="n">
-        <v>17</v>
-      </c>
       <c r="AQ7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS7" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AT7" t="n">
         <v>11</v>
@@ -1703,19 +1770,19 @@
         <v>27</v>
       </c>
       <c r="AV7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX7" t="n">
         <v>29</v>
       </c>
       <c r="AY7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AZ7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA7" t="n">
         <v>19</v>
@@ -1724,7 +1791,7 @@
         <v>23</v>
       </c>
       <c r="BC7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-18-2013-14</t>
+          <t>2014-02-18</t>
         </is>
       </c>
     </row>
@@ -1753,97 +1820,97 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E8" t="n">
         <v>32</v>
       </c>
       <c r="F8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G8" t="n">
-        <v>0.582</v>
+        <v>0.593</v>
       </c>
       <c r="H8" t="n">
         <v>48.1</v>
       </c>
       <c r="I8" t="n">
-        <v>39.2</v>
+        <v>39.3</v>
       </c>
       <c r="J8" t="n">
         <v>83.3</v>
       </c>
       <c r="K8" t="n">
-        <v>0.47</v>
+        <v>0.472</v>
       </c>
       <c r="L8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="N8" t="n">
-        <v>0.375</v>
+        <v>0.376</v>
       </c>
       <c r="O8" t="n">
-        <v>17.2</v>
+        <v>17</v>
       </c>
       <c r="P8" t="n">
-        <v>21.4</v>
+        <v>21.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.802</v>
+        <v>0.799</v>
       </c>
       <c r="R8" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>30.3</v>
+        <v>30.4</v>
       </c>
       <c r="T8" t="n">
-        <v>40.3</v>
+        <v>40.1</v>
       </c>
       <c r="U8" t="n">
         <v>23.3</v>
       </c>
       <c r="V8" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="W8" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Y8" t="n">
         <v>3.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AB8" t="n">
         <v>103.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE8" t="n">
         <v>8</v>
       </c>
       <c r="AF8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AH8" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AI8" t="n">
         <v>3</v>
@@ -1855,7 +1922,7 @@
         <v>6</v>
       </c>
       <c r="AL8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM8" t="n">
         <v>11</v>
@@ -1864,10 +1931,10 @@
         <v>6</v>
       </c>
       <c r="AO8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP8" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AQ8" t="n">
         <v>3</v>
@@ -1882,7 +1949,7 @@
         <v>28</v>
       </c>
       <c r="AU8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV8" t="n">
         <v>3</v>
@@ -1891,19 +1958,19 @@
         <v>6</v>
       </c>
       <c r="AX8" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AY8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA8" t="n">
         <v>23</v>
       </c>
       <c r="BB8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC8" t="n">
         <v>12</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-18-2013-14</t>
+          <t>2014-02-18</t>
         </is>
       </c>
     </row>
@@ -1935,64 +2002,64 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E9" t="n">
         <v>24</v>
       </c>
       <c r="F9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G9" t="n">
-        <v>0.462</v>
+        <v>0.471</v>
       </c>
       <c r="H9" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
       <c r="I9" t="n">
         <v>38</v>
       </c>
       <c r="J9" t="n">
-        <v>85</v>
+        <v>84.7</v>
       </c>
       <c r="K9" t="n">
-        <v>0.447</v>
+        <v>0.448</v>
       </c>
       <c r="L9" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="N9" t="n">
-        <v>0.357</v>
+        <v>0.361</v>
       </c>
       <c r="O9" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="P9" t="n">
-        <v>26</v>
+        <v>25.8</v>
       </c>
       <c r="Q9" t="n">
         <v>0.727</v>
       </c>
       <c r="R9" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="S9" t="n">
-        <v>33.2</v>
+        <v>33.1</v>
       </c>
       <c r="T9" t="n">
-        <v>45.5</v>
+        <v>45.3</v>
       </c>
       <c r="U9" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="V9" t="n">
         <v>15.5</v>
       </c>
       <c r="W9" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X9" t="n">
         <v>5.7</v>
@@ -2001,55 +2068,55 @@
         <v>5.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="AA9" t="n">
-        <v>21.4</v>
+        <v>21.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>103.1</v>
+        <v>103</v>
       </c>
       <c r="AC9" t="n">
         <v>-1.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AE9" t="n">
         <v>17</v>
       </c>
       <c r="AF9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH9" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AI9" t="n">
         <v>14</v>
       </c>
       <c r="AJ9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK9" t="n">
         <v>17</v>
       </c>
       <c r="AL9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AM9" t="n">
         <v>9</v>
       </c>
       <c r="AN9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AO9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ9" t="n">
         <v>26</v>
@@ -2061,16 +2128,16 @@
         <v>7</v>
       </c>
       <c r="AT9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AU9" t="n">
         <v>13</v>
       </c>
       <c r="AV9" t="n">
+        <v>24</v>
+      </c>
+      <c r="AW9" t="n">
         <v>23</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>22</v>
       </c>
       <c r="AX9" t="n">
         <v>5</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-18-2013-14</t>
+          <t>2014-02-18</t>
         </is>
       </c>
     </row>
@@ -2117,16 +2184,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E10" t="n">
         <v>22</v>
       </c>
       <c r="F10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G10" t="n">
-        <v>0.415</v>
+        <v>0.423</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
@@ -2135,10 +2202,10 @@
         <v>38.6</v>
       </c>
       <c r="J10" t="n">
-        <v>86.2</v>
+        <v>86</v>
       </c>
       <c r="K10" t="n">
-        <v>0.448</v>
+        <v>0.449</v>
       </c>
       <c r="L10" t="n">
         <v>6</v>
@@ -2153,25 +2220,25 @@
         <v>17.3</v>
       </c>
       <c r="P10" t="n">
-        <v>25.9</v>
+        <v>26</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.665</v>
+        <v>0.667</v>
       </c>
       <c r="R10" t="n">
         <v>14.7</v>
       </c>
       <c r="S10" t="n">
-        <v>30.6</v>
+        <v>30.5</v>
       </c>
       <c r="T10" t="n">
-        <v>45.3</v>
+        <v>45.2</v>
       </c>
       <c r="U10" t="n">
         <v>20.5</v>
       </c>
       <c r="V10" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W10" t="n">
         <v>8.9</v>
@@ -2183,34 +2250,34 @@
         <v>4.6</v>
       </c>
       <c r="Z10" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>100.5</v>
+        <v>100.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>-2.2</v>
+        <v>-2</v>
       </c>
       <c r="AD10" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AE10" t="n">
         <v>21</v>
       </c>
       <c r="AF10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG10" t="n">
         <v>21</v>
       </c>
       <c r="AH10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AJ10" t="n">
         <v>4</v>
@@ -2231,7 +2298,7 @@
         <v>16</v>
       </c>
       <c r="AP10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AQ10" t="n">
         <v>30</v>
@@ -2246,10 +2313,10 @@
         <v>7</v>
       </c>
       <c r="AU10" t="n">
+        <v>22</v>
+      </c>
+      <c r="AV10" t="n">
         <v>23</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>21</v>
       </c>
       <c r="AW10" t="n">
         <v>3</v>
@@ -2258,10 +2325,10 @@
         <v>9</v>
       </c>
       <c r="AY10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ10" t="n">
         <v>14</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>15</v>
       </c>
       <c r="BA10" t="n">
         <v>13</v>
@@ -2270,7 +2337,7 @@
         <v>14</v>
       </c>
       <c r="BC10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-18-2013-14</t>
+          <t>2014-02-18</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>4.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE11" t="n">
         <v>9</v>
@@ -2386,19 +2453,19 @@
         <v>9</v>
       </c>
       <c r="AG11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>6</v>
       </c>
-      <c r="AJ11" t="n">
+      <c r="AK11" t="n">
         <v>7</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>8</v>
       </c>
       <c r="AL11" t="n">
         <v>3</v>
@@ -2416,7 +2483,7 @@
         <v>20</v>
       </c>
       <c r="AQ11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR11" t="n">
         <v>15</v>
@@ -2437,7 +2504,7 @@
         <v>14</v>
       </c>
       <c r="AX11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-18-2013-14</t>
+          <t>2014-02-18</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>4.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE12" t="n">
         <v>6</v>
@@ -2571,7 +2638,7 @@
         <v>5</v>
       </c>
       <c r="AH12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI12" t="n">
         <v>16</v>
@@ -2589,7 +2656,7 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO12" t="n">
         <v>1</v>
@@ -2610,7 +2677,7 @@
         <v>8</v>
       </c>
       <c r="AU12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV12" t="n">
         <v>29</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-18-2013-14</t>
+          <t>2014-02-18</t>
         </is>
       </c>
     </row>
@@ -2663,28 +2730,28 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E13" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F13" t="n">
         <v>12</v>
       </c>
       <c r="G13" t="n">
-        <v>0.774</v>
+        <v>0.769</v>
       </c>
       <c r="H13" t="n">
         <v>48.3</v>
       </c>
       <c r="I13" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J13" t="n">
         <v>81</v>
       </c>
       <c r="K13" t="n">
-        <v>0.454</v>
+        <v>0.453</v>
       </c>
       <c r="L13" t="n">
         <v>6.9</v>
@@ -2693,55 +2760,55 @@
         <v>19.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0.352</v>
+        <v>0.351</v>
       </c>
       <c r="O13" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="P13" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.782</v>
+        <v>0.781</v>
       </c>
       <c r="R13" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="S13" t="n">
-        <v>35.2</v>
+        <v>35.3</v>
       </c>
       <c r="T13" t="n">
-        <v>45.4</v>
+        <v>45.6</v>
       </c>
       <c r="U13" t="n">
         <v>20.5</v>
       </c>
       <c r="V13" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W13" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X13" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="Y13" t="n">
         <v>4.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AA13" t="n">
         <v>21.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>98.7</v>
+        <v>98.5</v>
       </c>
       <c r="AC13" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD13" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AE13" t="n">
         <v>2</v>
@@ -2753,7 +2820,7 @@
         <v>2</v>
       </c>
       <c r="AH13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI13" t="n">
         <v>21</v>
@@ -2789,7 +2856,7 @@
         <v>1</v>
       </c>
       <c r="AT13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AU13" t="n">
         <v>22</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-18-2013-14</t>
+          <t>2014-02-18</t>
         </is>
       </c>
     </row>
@@ -2845,43 +2912,43 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E14" t="n">
         <v>37</v>
       </c>
       <c r="F14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G14" t="n">
-        <v>0.661</v>
+        <v>0.673</v>
       </c>
       <c r="H14" t="n">
         <v>48.3</v>
       </c>
       <c r="I14" t="n">
-        <v>38.6</v>
+        <v>38.7</v>
       </c>
       <c r="J14" t="n">
         <v>81.7</v>
       </c>
       <c r="K14" t="n">
-        <v>0.472</v>
+        <v>0.473</v>
       </c>
       <c r="L14" t="n">
         <v>8.1</v>
       </c>
       <c r="M14" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="N14" t="n">
-        <v>0.343</v>
+        <v>0.344</v>
       </c>
       <c r="O14" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="P14" t="n">
-        <v>29.7</v>
+        <v>29.6</v>
       </c>
       <c r="Q14" t="n">
         <v>0.73</v>
@@ -2893,40 +2960,40 @@
         <v>32.6</v>
       </c>
       <c r="T14" t="n">
-        <v>42.9</v>
+        <v>43</v>
       </c>
       <c r="U14" t="n">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="V14" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="W14" t="n">
         <v>8.4</v>
       </c>
       <c r="X14" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>106.9</v>
+        <v>107</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="AD14" t="n">
         <v>1</v>
       </c>
       <c r="AE14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF14" t="n">
         <v>7</v>
@@ -2935,10 +3002,10 @@
         <v>7</v>
       </c>
       <c r="AH14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ14" t="n">
         <v>23</v>
@@ -2953,7 +3020,7 @@
         <v>8</v>
       </c>
       <c r="AN14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO14" t="n">
         <v>2</v>
@@ -2968,7 +3035,7 @@
         <v>21</v>
       </c>
       <c r="AS14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT14" t="n">
         <v>16</v>
@@ -2998,7 +3065,7 @@
         <v>2</v>
       </c>
       <c r="BC14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-18-2013-14</t>
+          <t>2014-02-18</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-5.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE15" t="n">
         <v>26</v>
@@ -3117,7 +3184,7 @@
         <v>26</v>
       </c>
       <c r="AH15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI15" t="n">
         <v>18</v>
@@ -3138,7 +3205,7 @@
         <v>8</v>
       </c>
       <c r="AO15" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AP15" t="n">
         <v>19</v>
@@ -3180,7 +3247,7 @@
         <v>15</v>
       </c>
       <c r="BC15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-18-2013-14</t>
+          <t>2014-02-18</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F16" t="n">
         <v>23</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="H16" t="n">
         <v>48.4</v>
@@ -3227,10 +3294,10 @@
         <v>37.3</v>
       </c>
       <c r="J16" t="n">
-        <v>81.90000000000001</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L16" t="n">
         <v>4.9</v>
@@ -3239,10 +3306,10 @@
         <v>14.2</v>
       </c>
       <c r="N16" t="n">
-        <v>0.345</v>
+        <v>0.342</v>
       </c>
       <c r="O16" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="P16" t="n">
         <v>20.2</v>
@@ -3251,13 +3318,13 @@
         <v>0.75</v>
       </c>
       <c r="R16" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="S16" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="T16" t="n">
-        <v>42.4</v>
+        <v>42.5</v>
       </c>
       <c r="U16" t="n">
         <v>21.4</v>
@@ -3266,40 +3333,40 @@
         <v>13.5</v>
       </c>
       <c r="W16" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X16" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y16" t="n">
         <v>5.4</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>94.8</v>
+        <v>94.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AE16" t="n">
         <v>11</v>
       </c>
       <c r="AF16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG16" t="n">
         <v>11</v>
       </c>
       <c r="AH16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI16" t="n">
         <v>17</v>
@@ -3317,13 +3384,13 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AO16" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AQ16" t="n">
         <v>19</v>
@@ -3335,7 +3402,7 @@
         <v>22</v>
       </c>
       <c r="AT16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU16" t="n">
         <v>16</v>
@@ -3347,16 +3414,16 @@
         <v>16</v>
       </c>
       <c r="AX16" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AY16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ16" t="n">
         <v>7</v>
       </c>
       <c r="BA16" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BB16" t="n">
         <v>27</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-18-2013-14</t>
+          <t>2014-02-18</t>
         </is>
       </c>
     </row>
@@ -3391,34 +3458,34 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F17" t="n">
         <v>14</v>
       </c>
       <c r="G17" t="n">
-        <v>0.731</v>
+        <v>0.725</v>
       </c>
       <c r="H17" t="n">
         <v>48.5</v>
       </c>
       <c r="I17" t="n">
-        <v>39</v>
+        <v>38.9</v>
       </c>
       <c r="J17" t="n">
         <v>76.7</v>
       </c>
       <c r="K17" t="n">
-        <v>0.509</v>
+        <v>0.508</v>
       </c>
       <c r="L17" t="n">
         <v>8.1</v>
       </c>
       <c r="M17" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="N17" t="n">
         <v>0.37</v>
@@ -3430,22 +3497,22 @@
         <v>24</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.758</v>
+        <v>0.757</v>
       </c>
       <c r="R17" t="n">
         <v>7.3</v>
       </c>
       <c r="S17" t="n">
-        <v>29.3</v>
+        <v>29.5</v>
       </c>
       <c r="T17" t="n">
-        <v>36.6</v>
+        <v>36.7</v>
       </c>
       <c r="U17" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="V17" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W17" t="n">
         <v>9.199999999999999</v>
@@ -3454,22 +3521,22 @@
         <v>4.3</v>
       </c>
       <c r="Y17" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Z17" t="n">
         <v>20.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>104.4</v>
+        <v>104.1</v>
       </c>
       <c r="AC17" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AE17" t="n">
         <v>4</v>
@@ -3481,10 +3548,10 @@
         <v>3</v>
       </c>
       <c r="AH17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ17" t="n">
         <v>30</v>
@@ -3499,13 +3566,13 @@
         <v>13</v>
       </c>
       <c r="AN17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO17" t="n">
         <v>12</v>
       </c>
       <c r="AP17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AQ17" t="n">
         <v>16</v>
@@ -3529,13 +3596,13 @@
         <v>1</v>
       </c>
       <c r="AX17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
       </c>
       <c r="AZ17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA17" t="n">
         <v>12</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-18-2013-14</t>
+          <t>2014-02-18</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F18" t="n">
         <v>43</v>
       </c>
       <c r="G18" t="n">
-        <v>0.189</v>
+        <v>0.173</v>
       </c>
       <c r="H18" t="n">
         <v>48.7</v>
@@ -3597,19 +3664,19 @@
         <v>0.423</v>
       </c>
       <c r="L18" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="M18" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="N18" t="n">
-        <v>0.354</v>
+        <v>0.352</v>
       </c>
       <c r="O18" t="n">
-        <v>15.3</v>
+        <v>15.1</v>
       </c>
       <c r="P18" t="n">
-        <v>20.3</v>
+        <v>20.1</v>
       </c>
       <c r="Q18" t="n">
         <v>0.753</v>
@@ -3621,37 +3688,37 @@
         <v>29.7</v>
       </c>
       <c r="T18" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="U18" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="V18" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="W18" t="n">
         <v>6.9</v>
       </c>
       <c r="X18" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Y18" t="n">
         <v>5.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AA18" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>92.5</v>
+        <v>92.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3678,7 +3745,7 @@
         <v>18</v>
       </c>
       <c r="AM18" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AN18" t="n">
         <v>18</v>
@@ -3687,7 +3754,7 @@
         <v>28</v>
       </c>
       <c r="AP18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ18" t="n">
         <v>18</v>
@@ -3705,7 +3772,7 @@
         <v>17</v>
       </c>
       <c r="AV18" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AW18" t="n">
         <v>27</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-18-2013-14</t>
+          <t>2014-02-18</t>
         </is>
       </c>
     </row>
@@ -3833,22 +3900,22 @@
         <v>3.7</v>
       </c>
       <c r="AD19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE19" t="n">
         <v>14</v>
       </c>
       <c r="AF19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG19" t="n">
         <v>16</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>15</v>
       </c>
       <c r="AH19" t="n">
         <v>25</v>
       </c>
       <c r="AI19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ19" t="n">
         <v>2</v>
@@ -3863,7 +3930,7 @@
         <v>12</v>
       </c>
       <c r="AN19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO19" t="n">
         <v>3</v>
@@ -3884,7 +3951,7 @@
         <v>3</v>
       </c>
       <c r="AU19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV19" t="n">
         <v>7</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-18-2013-14</t>
+          <t>2014-02-18</t>
         </is>
       </c>
     </row>
@@ -4015,16 +4082,16 @@
         <v>-1.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="AE20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF20" t="n">
         <v>19</v>
       </c>
       <c r="AG20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH20" t="n">
         <v>13</v>
@@ -4051,7 +4118,7 @@
         <v>15</v>
       </c>
       <c r="AP20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ20" t="n">
         <v>12</v>
@@ -4063,7 +4130,7 @@
         <v>26</v>
       </c>
       <c r="AT20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU20" t="n">
         <v>15</v>
@@ -4072,13 +4139,13 @@
         <v>6</v>
       </c>
       <c r="AW20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX20" t="n">
         <v>1</v>
       </c>
       <c r="AY20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AZ20" t="n">
         <v>27</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-18-2013-14</t>
+          <t>2014-02-18</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E21" t="n">
         <v>20</v>
       </c>
       <c r="F21" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G21" t="n">
-        <v>0.377</v>
+        <v>0.385</v>
       </c>
       <c r="H21" t="n">
         <v>48.5</v>
@@ -4149,28 +4216,28 @@
         <v>24.3</v>
       </c>
       <c r="N21" t="n">
-        <v>0.364</v>
+        <v>0.367</v>
       </c>
       <c r="O21" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="P21" t="n">
         <v>19.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.75</v>
+        <v>0.748</v>
       </c>
       <c r="R21" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S21" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="T21" t="n">
         <v>40.7</v>
       </c>
       <c r="U21" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="V21" t="n">
         <v>13.1</v>
@@ -4191,22 +4258,22 @@
         <v>19.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>97.2</v>
+        <v>97.3</v>
       </c>
       <c r="AC21" t="n">
-        <v>-1.9</v>
+        <v>-1.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AE21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF21" t="n">
         <v>22</v>
       </c>
       <c r="AG21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH21" t="n">
         <v>10</v>
@@ -4227,7 +4294,7 @@
         <v>6</v>
       </c>
       <c r="AN21" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AO21" t="n">
         <v>30</v>
@@ -4236,7 +4303,7 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR21" t="n">
         <v>19</v>
@@ -4245,10 +4312,10 @@
         <v>28</v>
       </c>
       <c r="AT21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AU21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV21" t="n">
         <v>2</v>
@@ -4260,7 +4327,7 @@
         <v>19</v>
       </c>
       <c r="AY21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ21" t="n">
         <v>26</v>
@@ -4269,7 +4336,7 @@
         <v>22</v>
       </c>
       <c r="BB21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC21" t="n">
         <v>19</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-18-2013-14</t>
+          <t>2014-02-18</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>7.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4406,16 +4473,16 @@
         <v>17</v>
       </c>
       <c r="AM22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AN22" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AO22" t="n">
         <v>5</v>
       </c>
       <c r="AP22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ22" t="n">
         <v>2</v>
@@ -4451,7 +4518,7 @@
         <v>18</v>
       </c>
       <c r="BB22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC22" t="n">
         <v>2</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-18-2013-14</t>
+          <t>2014-02-18</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E23" t="n">
         <v>16</v>
       </c>
       <c r="F23" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G23" t="n">
-        <v>0.291</v>
+        <v>0.296</v>
       </c>
       <c r="H23" t="n">
         <v>48.6</v>
@@ -4501,40 +4568,40 @@
         <v>36.3</v>
       </c>
       <c r="J23" t="n">
-        <v>82.2</v>
+        <v>82.3</v>
       </c>
       <c r="K23" t="n">
-        <v>0.442</v>
+        <v>0.441</v>
       </c>
       <c r="L23" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="M23" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="N23" t="n">
-        <v>0.351</v>
+        <v>0.349</v>
       </c>
       <c r="O23" t="n">
-        <v>16.3</v>
+        <v>16.5</v>
       </c>
       <c r="P23" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.761</v>
+        <v>0.764</v>
       </c>
       <c r="R23" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="S23" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="T23" t="n">
         <v>42.1</v>
       </c>
       <c r="U23" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V23" t="n">
         <v>14.9</v>
@@ -4543,7 +4610,7 @@
         <v>7.6</v>
       </c>
       <c r="X23" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Y23" t="n">
         <v>5.9</v>
@@ -4555,13 +4622,13 @@
         <v>18.8</v>
       </c>
       <c r="AB23" t="n">
-        <v>96.09999999999999</v>
+        <v>96</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.3</v>
+        <v>-5.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE23" t="n">
         <v>28</v>
@@ -4576,10 +4643,10 @@
         <v>5</v>
       </c>
       <c r="AI23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK23" t="n">
         <v>21</v>
@@ -4588,10 +4655,10 @@
         <v>20</v>
       </c>
       <c r="AM23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AN23" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AO23" t="n">
         <v>22</v>
@@ -4600,13 +4667,13 @@
         <v>22</v>
       </c>
       <c r="AQ23" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AR23" t="n">
         <v>25</v>
       </c>
       <c r="AS23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT23" t="n">
         <v>22</v>
@@ -4621,7 +4688,7 @@
         <v>15</v>
       </c>
       <c r="AX23" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AY23" t="n">
         <v>26</v>
@@ -4630,7 +4697,7 @@
         <v>8</v>
       </c>
       <c r="BA23" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BB23" t="n">
         <v>24</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-18-2013-14</t>
+          <t>2014-02-18</t>
         </is>
       </c>
     </row>
@@ -4665,52 +4732,52 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E24" t="n">
         <v>15</v>
       </c>
       <c r="F24" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G24" t="n">
-        <v>0.273</v>
+        <v>0.278</v>
       </c>
       <c r="H24" t="n">
         <v>48.6</v>
       </c>
       <c r="I24" t="n">
-        <v>38.3</v>
+        <v>38.4</v>
       </c>
       <c r="J24" t="n">
         <v>88.3</v>
       </c>
       <c r="K24" t="n">
-        <v>0.434</v>
+        <v>0.435</v>
       </c>
       <c r="L24" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="M24" t="n">
         <v>21.8</v>
       </c>
       <c r="N24" t="n">
-        <v>0.313</v>
+        <v>0.314</v>
       </c>
       <c r="O24" t="n">
         <v>16.6</v>
       </c>
       <c r="P24" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.715</v>
+        <v>0.716</v>
       </c>
       <c r="R24" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="S24" t="n">
-        <v>32.6</v>
+        <v>32.7</v>
       </c>
       <c r="T24" t="n">
         <v>44.5</v>
@@ -4722,13 +4789,13 @@
         <v>17.4</v>
       </c>
       <c r="W24" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="X24" t="n">
         <v>4.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="Z24" t="n">
         <v>21.8</v>
@@ -4737,13 +4804,13 @@
         <v>20.6</v>
       </c>
       <c r="AB24" t="n">
-        <v>100</v>
+        <v>100.3</v>
       </c>
       <c r="AC24" t="n">
-        <v>-10.5</v>
+        <v>-10.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE24" t="n">
         <v>29</v>
@@ -4758,7 +4825,7 @@
         <v>6</v>
       </c>
       <c r="AI24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ24" t="n">
         <v>1</v>
@@ -4779,16 +4846,16 @@
         <v>20</v>
       </c>
       <c r="AP24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ24" t="n">
         <v>28</v>
       </c>
       <c r="AR24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-18-2013-14</t>
+          <t>2014-02-18</t>
         </is>
       </c>
     </row>
@@ -4847,28 +4914,28 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E25" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F25" t="n">
         <v>21</v>
       </c>
       <c r="G25" t="n">
-        <v>0.596</v>
+        <v>0.588</v>
       </c>
       <c r="H25" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="I25" t="n">
         <v>38.6</v>
       </c>
       <c r="J25" t="n">
-        <v>84.40000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="K25" t="n">
-        <v>0.457</v>
+        <v>0.459</v>
       </c>
       <c r="L25" t="n">
         <v>9.4</v>
@@ -4880,22 +4947,22 @@
         <v>0.37</v>
       </c>
       <c r="O25" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="P25" t="n">
-        <v>24.2</v>
+        <v>23.9</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.765</v>
+        <v>0.764</v>
       </c>
       <c r="R25" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="S25" t="n">
-        <v>32</v>
+        <v>31.8</v>
       </c>
       <c r="T25" t="n">
-        <v>43.6</v>
+        <v>43.3</v>
       </c>
       <c r="U25" t="n">
         <v>19.1</v>
@@ -4910,37 +4977,37 @@
         <v>4.9</v>
       </c>
       <c r="Y25" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Z25" t="n">
-        <v>22.1</v>
+        <v>21.9</v>
       </c>
       <c r="AA25" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AB25" t="n">
-        <v>105.1</v>
+        <v>104.9</v>
       </c>
       <c r="AC25" t="n">
         <v>3.1</v>
       </c>
       <c r="AD25" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AE25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF25" t="n">
         <v>8</v>
       </c>
       <c r="AG25" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI25" t="n">
         <v>8</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>9</v>
       </c>
       <c r="AJ25" t="n">
         <v>9</v>
@@ -4949,22 +5016,22 @@
         <v>9</v>
       </c>
       <c r="AL25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM25" t="n">
         <v>2</v>
       </c>
       <c r="AN25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO25" t="n">
         <v>10</v>
       </c>
       <c r="AP25" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AQ25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR25" t="n">
         <v>12</v>
@@ -4973,7 +5040,7 @@
         <v>15</v>
       </c>
       <c r="AT25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU25" t="n">
         <v>30</v>
@@ -4982,7 +5049,7 @@
         <v>18</v>
       </c>
       <c r="AW25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX25" t="n">
         <v>13</v>
@@ -4994,10 +5061,10 @@
         <v>24</v>
       </c>
       <c r="BA25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-18-2013-14</t>
+          <t>2014-02-18</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>4.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE26" t="n">
         <v>6</v>
@@ -5119,7 +5186,7 @@
         <v>5</v>
       </c>
       <c r="AH26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI26" t="n">
         <v>2</v>
@@ -5131,7 +5198,7 @@
         <v>13</v>
       </c>
       <c r="AL26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM26" t="n">
         <v>5</v>
@@ -5143,13 +5210,13 @@
         <v>6</v>
       </c>
       <c r="AP26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AQ26" t="n">
         <v>1</v>
       </c>
       <c r="AR26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS26" t="n">
         <v>6</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-18-2013-14</t>
+          <t>2014-02-18</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-2.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE27" t="n">
         <v>26</v>
@@ -5301,7 +5368,7 @@
         <v>26</v>
       </c>
       <c r="AH27" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AI27" t="n">
         <v>19</v>
@@ -5319,7 +5386,7 @@
         <v>24</v>
       </c>
       <c r="AN27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO27" t="n">
         <v>4</v>
@@ -5331,7 +5398,7 @@
         <v>7</v>
       </c>
       <c r="AR27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS27" t="n">
         <v>16</v>
@@ -5343,7 +5410,7 @@
         <v>29</v>
       </c>
       <c r="AV27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW27" t="n">
         <v>21</v>
@@ -5364,7 +5431,7 @@
         <v>13</v>
       </c>
       <c r="BC27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-18-2013-14</t>
+          <t>2014-02-18</t>
         </is>
       </c>
     </row>
@@ -5393,25 +5460,25 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E28" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F28" t="n">
         <v>15</v>
       </c>
       <c r="G28" t="n">
-        <v>0.722</v>
+        <v>0.717</v>
       </c>
       <c r="H28" t="n">
         <v>48.3</v>
       </c>
       <c r="I28" t="n">
-        <v>40.3</v>
+        <v>40.2</v>
       </c>
       <c r="J28" t="n">
-        <v>82.2</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K28" t="n">
         <v>0.49</v>
@@ -5423,7 +5490,7 @@
         <v>20.4</v>
       </c>
       <c r="N28" t="n">
-        <v>0.394</v>
+        <v>0.393</v>
       </c>
       <c r="O28" t="n">
         <v>15.3</v>
@@ -5438,10 +5505,10 @@
         <v>8.9</v>
       </c>
       <c r="S28" t="n">
-        <v>33.5</v>
+        <v>33.4</v>
       </c>
       <c r="T28" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="U28" t="n">
         <v>24.7</v>
@@ -5459,19 +5526,19 @@
         <v>4.8</v>
       </c>
       <c r="Z28" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="AA28" t="n">
         <v>19.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>104</v>
+        <v>103.8</v>
       </c>
       <c r="AC28" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE28" t="n">
         <v>3</v>
@@ -5483,19 +5550,19 @@
         <v>4</v>
       </c>
       <c r="AH28" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AI28" t="n">
         <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
       </c>
       <c r="AL28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM28" t="n">
         <v>19</v>
@@ -5519,7 +5586,7 @@
         <v>5</v>
       </c>
       <c r="AT28" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AU28" t="n">
         <v>2</v>
@@ -5531,10 +5598,10 @@
         <v>17</v>
       </c>
       <c r="AX28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ28" t="n">
         <v>2</v>
@@ -5543,10 +5610,10 @@
         <v>25</v>
       </c>
       <c r="BB28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-18-2013-14</t>
+          <t>2014-02-18</t>
         </is>
       </c>
     </row>
@@ -5575,64 +5642,64 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E29" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F29" t="n">
         <v>24</v>
       </c>
       <c r="G29" t="n">
-        <v>0.547</v>
+        <v>0.538</v>
       </c>
       <c r="H29" t="n">
         <v>48.5</v>
       </c>
       <c r="I29" t="n">
-        <v>36.2</v>
+        <v>36.1</v>
       </c>
       <c r="J29" t="n">
-        <v>82.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>0.439</v>
+        <v>0.437</v>
       </c>
       <c r="L29" t="n">
         <v>8.4</v>
       </c>
       <c r="M29" t="n">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
       <c r="N29" t="n">
-        <v>0.365</v>
+        <v>0.364</v>
       </c>
       <c r="O29" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="P29" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="Q29" t="n">
         <v>0.773</v>
       </c>
       <c r="R29" t="n">
-        <v>11.9</v>
+        <v>12.1</v>
       </c>
       <c r="S29" t="n">
-        <v>31.2</v>
+        <v>31.3</v>
       </c>
       <c r="T29" t="n">
-        <v>43.1</v>
+        <v>43.4</v>
       </c>
       <c r="U29" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="V29" t="n">
         <v>14</v>
       </c>
       <c r="W29" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="X29" t="n">
         <v>4.3</v>
@@ -5650,10 +5717,10 @@
         <v>99.7</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AE29" t="n">
         <v>12</v>
@@ -5674,7 +5741,7 @@
         <v>17</v>
       </c>
       <c r="AK29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL29" t="n">
         <v>8</v>
@@ -5683,25 +5750,25 @@
         <v>10</v>
       </c>
       <c r="AN29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP29" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AQ29" t="n">
         <v>9</v>
       </c>
       <c r="AR29" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AS29" t="n">
         <v>21</v>
       </c>
       <c r="AT29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU29" t="n">
         <v>18</v>
@@ -5710,7 +5777,7 @@
         <v>9</v>
       </c>
       <c r="AW29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX29" t="n">
         <v>23</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-18-2013-14</t>
+          <t>2014-02-18</t>
         </is>
       </c>
     </row>
@@ -5835,13 +5902,13 @@
         <v>-5.9</v>
       </c>
       <c r="AD30" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="AE30" t="n">
         <v>24</v>
       </c>
       <c r="AF30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG30" t="n">
         <v>24</v>
@@ -5856,7 +5923,7 @@
         <v>25</v>
       </c>
       <c r="AK30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL30" t="n">
         <v>24</v>
@@ -5865,7 +5932,7 @@
         <v>26</v>
       </c>
       <c r="AN30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO30" t="n">
         <v>23</v>
@@ -5874,7 +5941,7 @@
         <v>21</v>
       </c>
       <c r="AQ30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR30" t="n">
         <v>16</v>
@@ -5892,13 +5959,13 @@
         <v>12</v>
       </c>
       <c r="AW30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX30" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY30" t="n">
         <v>18</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>17</v>
       </c>
       <c r="AZ30" t="n">
         <v>18</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-18-2013-14</t>
+          <t>2014-02-18</t>
         </is>
       </c>
     </row>
@@ -5939,37 +6006,37 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E31" t="n">
         <v>25</v>
       </c>
       <c r="F31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G31" t="n">
-        <v>0.472</v>
+        <v>0.481</v>
       </c>
       <c r="H31" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="I31" t="n">
         <v>38</v>
       </c>
       <c r="J31" t="n">
-        <v>84.40000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="K31" t="n">
-        <v>0.45</v>
+        <v>0.449</v>
       </c>
       <c r="L31" t="n">
         <v>7.8</v>
       </c>
       <c r="M31" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="N31" t="n">
-        <v>0.378</v>
+        <v>0.38</v>
       </c>
       <c r="O31" t="n">
         <v>15.5</v>
@@ -5978,52 +6045,52 @@
         <v>21.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.728</v>
+        <v>0.73</v>
       </c>
       <c r="R31" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S31" t="n">
-        <v>31.5</v>
+        <v>31.6</v>
       </c>
       <c r="T31" t="n">
         <v>42.4</v>
       </c>
       <c r="U31" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="V31" t="n">
         <v>14.9</v>
       </c>
       <c r="W31" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X31" t="n">
         <v>4.8</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="AB31" t="n">
-        <v>99.2</v>
+        <v>99.3</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.4</v>
+        <v>-0.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AE31" t="n">
         <v>14</v>
       </c>
       <c r="AF31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG31" t="n">
         <v>15</v>
@@ -6053,7 +6120,7 @@
         <v>26</v>
       </c>
       <c r="AP31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ31" t="n">
         <v>25</v>
@@ -6062,10 +6129,10 @@
         <v>20</v>
       </c>
       <c r="AS31" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AT31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU31" t="n">
         <v>9</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-18-2013-14</t>
+          <t>2014-02-18</t>
         </is>
       </c>
     </row>
